--- a/docs/Mapping_casi_uso/cittadinanza/Citt_026.xlsx
+++ b/docs/Mapping_casi_uso/cittadinanza/Citt_026.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="532" uniqueCount="144">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="539" uniqueCount="146">
   <si>
     <t>Sezione</t>
   </si>
@@ -276,6 +276,12 @@
   </si>
   <si>
     <t>nomeComuneAIRE</t>
+  </si>
+  <si>
+    <t>Residenza al momento dell'evento originario</t>
+  </si>
+  <si>
+    <t>residenzaOriginaria</t>
   </si>
   <si>
     <t>flag dichiarante</t>
@@ -502,11 +508,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:H76"/>
+  <dimension ref="A1:H77"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="25.80859375" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="38.875" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="40.984375" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="12.5625" customWidth="true" bestFit="true"/>
     <col min="4" max="4" width="47.4296875" customWidth="true" bestFit="true"/>
     <col min="5" max="5" width="25.734375" customWidth="true" bestFit="true"/>
@@ -1373,7 +1379,7 @@
         <v>88</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D38" s="2" t="s">
         <v>34</v>
@@ -1436,53 +1442,53 @@
     </row>
     <row r="41">
       <c r="A41" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="B41" s="2" t="s">
+      <c r="C41" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E41" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D41" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E41" s="2" t="s">
-        <v>97</v>
-      </c>
       <c r="F41" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G41" s="2" t="s">
-        <v>98</v>
+        <v>18</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B42" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E42" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>33</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>96</v>
-      </c>
-      <c r="E42" s="2" t="s">
+      <c r="F42" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G42" s="2" t="s">
         <v>100</v>
-      </c>
-      <c r="F42" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G42" s="2" t="s">
-        <v>98</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B43" s="2" t="s">
         <v>101</v>
@@ -1491,7 +1497,7 @@
         <v>33</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E43" s="2" t="s">
         <v>102</v>
@@ -1500,12 +1506,12 @@
         <v>10</v>
       </c>
       <c r="G43" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B44" s="2" t="s">
         <v>103</v>
@@ -1514,7 +1520,7 @@
         <v>33</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E44" s="2" t="s">
         <v>104</v>
@@ -1523,12 +1529,12 @@
         <v>10</v>
       </c>
       <c r="G44" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B45" s="2" t="s">
         <v>105</v>
@@ -1537,7 +1543,7 @@
         <v>33</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E45" s="2" t="s">
         <v>106</v>
@@ -1546,12 +1552,12 @@
         <v>10</v>
       </c>
       <c r="G45" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B46" s="2" t="s">
         <v>107</v>
@@ -1560,44 +1566,44 @@
         <v>33</v>
       </c>
       <c r="D46" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E46" s="2" t="s">
-        <v>17</v>
+        <v>108</v>
       </c>
       <c r="F46" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G46" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B47" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C47" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D47" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E47" s="2" t="s">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="F47" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G47" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B48" s="2" t="s">
         <v>110</v>
@@ -1606,44 +1612,44 @@
         <v>33</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E48" s="2" t="s">
-        <v>20</v>
+        <v>111</v>
       </c>
       <c r="F48" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G48" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B49" s="2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D49" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E49" s="2" t="s">
-        <v>112</v>
+        <v>20</v>
       </c>
       <c r="F49" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G49" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B50" s="2" t="s">
         <v>113</v>
@@ -1652,7 +1658,7 @@
         <v>33</v>
       </c>
       <c r="D50" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E50" s="2" t="s">
         <v>114</v>
@@ -1661,12 +1667,12 @@
         <v>10</v>
       </c>
       <c r="G50" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B51" s="2" t="s">
         <v>115</v>
@@ -1675,7 +1681,7 @@
         <v>33</v>
       </c>
       <c r="D51" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E51" s="2" t="s">
         <v>116</v>
@@ -1684,12 +1690,12 @@
         <v>10</v>
       </c>
       <c r="G51" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="B52" s="2" t="s">
         <v>117</v>
@@ -1698,7 +1704,7 @@
         <v>33</v>
       </c>
       <c r="D52" s="2" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="E52" s="2" t="s">
         <v>118</v>
@@ -1707,44 +1713,44 @@
         <v>10</v>
       </c>
       <c r="G52" s="2" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="s">
+        <v>96</v>
+      </c>
+      <c r="B53" s="2" t="s">
         <v>119</v>
       </c>
-      <c r="B53" s="2" t="s">
+      <c r="C53" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D53" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E53" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="C53" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D53" s="2" t="s">
-        <v>121</v>
-      </c>
-      <c r="E53" s="2" t="s">
-        <v>122</v>
-      </c>
       <c r="F53" s="2" t="s">
         <v>10</v>
       </c>
       <c r="G53" s="2" t="s">
-        <v>18</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B54" s="2" t="s">
+        <v>122</v>
+      </c>
+      <c r="C54" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="D54" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="C54" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D54" s="2" t="s">
-        <v>121</v>
       </c>
       <c r="E54" s="2" t="s">
         <v>124</v>
@@ -1758,7 +1764,7 @@
     </row>
     <row r="55">
       <c r="A55" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B55" s="2" t="s">
         <v>125</v>
@@ -1767,7 +1773,7 @@
         <v>9</v>
       </c>
       <c r="D55" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E55" s="2" t="s">
         <v>126</v>
@@ -1781,7 +1787,7 @@
     </row>
     <row r="56">
       <c r="A56" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B56" s="2" t="s">
         <v>127</v>
@@ -1790,7 +1796,7 @@
         <v>9</v>
       </c>
       <c r="D56" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E56" s="2" t="s">
         <v>128</v>
@@ -1804,7 +1810,7 @@
     </row>
     <row r="57">
       <c r="A57" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B57" s="2" t="s">
         <v>129</v>
@@ -1813,7 +1819,7 @@
         <v>9</v>
       </c>
       <c r="D57" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E57" s="2" t="s">
         <v>130</v>
@@ -1827,16 +1833,16 @@
     </row>
     <row r="58">
       <c r="A58" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B58" s="2" t="s">
         <v>131</v>
       </c>
       <c r="C58" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D58" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E58" s="2" t="s">
         <v>132</v>
@@ -1850,7 +1856,7 @@
     </row>
     <row r="59">
       <c r="A59" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B59" s="2" t="s">
         <v>133</v>
@@ -1859,7 +1865,7 @@
         <v>33</v>
       </c>
       <c r="D59" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E59" s="2" t="s">
         <v>134</v>
@@ -1873,7 +1879,7 @@
     </row>
     <row r="60">
       <c r="A60" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B60" s="2" t="s">
         <v>135</v>
@@ -1882,7 +1888,7 @@
         <v>33</v>
       </c>
       <c r="D60" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E60" s="2" t="s">
         <v>136</v>
@@ -1896,7 +1902,7 @@
     </row>
     <row r="61">
       <c r="A61" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B61" s="2" t="s">
         <v>137</v>
@@ -1905,7 +1911,7 @@
         <v>33</v>
       </c>
       <c r="D61" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E61" s="2" t="s">
         <v>138</v>
@@ -1919,19 +1925,19 @@
     </row>
     <row r="62">
       <c r="A62" s="2" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>58</v>
+        <v>139</v>
       </c>
       <c r="C62" s="2" t="s">
         <v>33</v>
       </c>
       <c r="D62" s="2" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="E62" s="2" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="F62" s="2" t="s">
         <v>10</v>
@@ -1942,19 +1948,19 @@
     </row>
     <row r="63">
       <c r="A63" s="2" t="s">
-        <v>140</v>
+        <v>121</v>
       </c>
       <c r="B63" s="2" t="s">
-        <v>120</v>
+        <v>58</v>
       </c>
       <c r="C63" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D63" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="E63" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="E63" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="F63" s="2" t="s">
         <v>10</v>
@@ -1965,16 +1971,16 @@
     </row>
     <row r="64">
       <c r="A64" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C64" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D64" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E64" s="2" t="s">
         <v>124</v>
@@ -1988,7 +1994,7 @@
     </row>
     <row r="65">
       <c r="A65" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B65" s="2" t="s">
         <v>125</v>
@@ -1997,7 +2003,7 @@
         <v>9</v>
       </c>
       <c r="D65" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E65" s="2" t="s">
         <v>126</v>
@@ -2011,19 +2017,19 @@
     </row>
     <row r="66">
       <c r="A66" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C66" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D66" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E66" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F66" s="2" t="s">
         <v>10</v>
@@ -2034,7 +2040,7 @@
     </row>
     <row r="67">
       <c r="A67" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B67" s="2" t="s">
         <v>133</v>
@@ -2043,7 +2049,7 @@
         <v>9</v>
       </c>
       <c r="D67" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E67" s="2" t="s">
         <v>134</v>
@@ -2057,7 +2063,7 @@
     </row>
     <row r="68">
       <c r="A68" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B68" s="2" t="s">
         <v>135</v>
@@ -2066,7 +2072,7 @@
         <v>9</v>
       </c>
       <c r="D68" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E68" s="2" t="s">
         <v>136</v>
@@ -2080,7 +2086,7 @@
     </row>
     <row r="69">
       <c r="A69" s="2" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B69" s="2" t="s">
         <v>137</v>
@@ -2089,7 +2095,7 @@
         <v>9</v>
       </c>
       <c r="D69" s="2" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E69" s="2" t="s">
         <v>138</v>
@@ -2106,7 +2112,7 @@
         <v>142</v>
       </c>
       <c r="B70" s="2" t="s">
-        <v>120</v>
+        <v>139</v>
       </c>
       <c r="C70" s="2" t="s">
         <v>9</v>
@@ -2115,7 +2121,7 @@
         <v>143</v>
       </c>
       <c r="E70" s="2" t="s">
-        <v>122</v>
+        <v>140</v>
       </c>
       <c r="F70" s="2" t="s">
         <v>10</v>
@@ -2126,16 +2132,16 @@
     </row>
     <row r="71">
       <c r="A71" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="C71" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D71" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E71" s="2" t="s">
         <v>124</v>
@@ -2149,7 +2155,7 @@
     </row>
     <row r="72">
       <c r="A72" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B72" s="2" t="s">
         <v>125</v>
@@ -2158,7 +2164,7 @@
         <v>9</v>
       </c>
       <c r="D72" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E72" s="2" t="s">
         <v>126</v>
@@ -2172,19 +2178,19 @@
     </row>
     <row r="73">
       <c r="A73" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="C73" s="2" t="s">
         <v>9</v>
       </c>
       <c r="D73" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E73" s="2" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="F73" s="2" t="s">
         <v>10</v>
@@ -2195,16 +2201,16 @@
     </row>
     <row r="74">
       <c r="A74" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B74" s="2" t="s">
         <v>133</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D74" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E74" s="2" t="s">
         <v>134</v>
@@ -2218,16 +2224,16 @@
     </row>
     <row r="75">
       <c r="A75" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B75" s="2" t="s">
         <v>135</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="D75" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E75" s="2" t="s">
         <v>136</v>
@@ -2241,16 +2247,16 @@
     </row>
     <row r="76">
       <c r="A76" s="2" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="B76" s="2" t="s">
         <v>137</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>33</v>
+        <v>9</v>
       </c>
       <c r="D76" s="2" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E76" s="2" t="s">
         <v>138</v>
@@ -2259,6 +2265,29 @@
         <v>10</v>
       </c>
       <c r="G76" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="B77" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="C77" s="2" t="s">
+        <v>33</v>
+      </c>
+      <c r="D77" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E77" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="F77" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G77" s="2" t="s">
         <v>18</v>
       </c>
     </row>
